--- a/data/trans_orig/IP2906_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP2906_2023-Edad-trans_orig.xlsx
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13637</t>
+          <t>13796</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23786</t>
+          <t>23792</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>28,54%</t>
+          <t>28,88%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>49,79%</t>
+          <t>49,8%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>15193</t>
+          <t>15046</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>25603</t>
+          <t>25183</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>33,23%</t>
+          <t>32,91%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>56,0%</t>
+          <t>55,08%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>32537</t>
+          <t>31969</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>46638</t>
+          <t>47074</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>34,8%</t>
+          <t>34,19%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>49,88%</t>
+          <t>50,35%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>23990</t>
+          <t>23984</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>34139</t>
+          <t>33980</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>50,21%</t>
+          <t>50,2%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>71,46%</t>
+          <t>71,12%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>20119</t>
+          <t>20539</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>30529</t>
+          <t>30676</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>44,0%</t>
+          <t>44,92%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>66,77%</t>
+          <t>67,09%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>46860</t>
+          <t>46424</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>60961</t>
+          <t>61529</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>50,12%</t>
+          <t>49,65%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>65,2%</t>
+          <t>65,81%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>64423</t>
+          <t>65293</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>86247</t>
+          <t>86753</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>40,76%</t>
+          <t>41,31%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>54,57%</t>
+          <t>54,89%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>73305</t>
+          <t>73150</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>95640</t>
+          <t>95750</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>40,49%</t>
+          <t>40,4%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>52,83%</t>
+          <t>52,89%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>144321</t>
+          <t>144189</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>175403</t>
+          <t>174302</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>42,56%</t>
+          <t>42,52%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>51,73%</t>
+          <t>51,4%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>71805</t>
+          <t>71299</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>93629</t>
+          <t>92759</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>45,43%</t>
+          <t>45,11%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>59,24%</t>
+          <t>58,69%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>85408</t>
+          <t>85298</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>107743</t>
+          <t>107898</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>47,17%</t>
+          <t>47,11%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>59,51%</t>
+          <t>59,6%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>163697</t>
+          <t>164798</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>194779</t>
+          <t>194911</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>48,27%</t>
+          <t>48,6%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>57,44%</t>
+          <t>57,48%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>57889</t>
+          <t>57590</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>80381</t>
+          <t>80408</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>33,75%</t>
+          <t>33,57%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>46,86%</t>
+          <t>46,88%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>74031</t>
+          <t>74326</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>101682</t>
+          <t>101320</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>34,84%</t>
+          <t>34,98%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>47,85%</t>
+          <t>47,68%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>139152</t>
+          <t>137751</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>174728</t>
+          <t>175477</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>36,24%</t>
+          <t>35,87%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>45,5%</t>
+          <t>45,69%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>91147</t>
+          <t>91120</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>113639</t>
+          <t>113938</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>53,14%</t>
+          <t>53,12%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>66,25%</t>
+          <t>66,43%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>110808</t>
+          <t>111170</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>138459</t>
+          <t>138164</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>52,15%</t>
+          <t>52,32%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>65,16%</t>
+          <t>65,02%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>209290</t>
+          <t>208541</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>244866</t>
+          <t>246267</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>54,5%</t>
+          <t>54,31%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>63,76%</t>
+          <t>64,13%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>89563</t>
+          <t>91311</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>118892</t>
+          <t>118628</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>37,25%</t>
+          <t>37,98%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>49,45%</t>
+          <t>49,34%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>102312</t>
+          <t>102837</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>142444</t>
+          <t>141819</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>34,13%</t>
+          <t>34,3%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>47,52%</t>
+          <t>47,31%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>205092</t>
+          <t>202198</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>254194</t>
+          <t>250863</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>37,97%</t>
+          <t>37,43%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>47,06%</t>
+          <t>46,44%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>121527</t>
+          <t>121791</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>150856</t>
+          <t>149108</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>50,55%</t>
+          <t>50,66%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>62,75%</t>
+          <t>62,02%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>157340</t>
+          <t>157965</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>197472</t>
+          <t>196947</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>52,48%</t>
+          <t>52,69%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>65,87%</t>
+          <t>65,7%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>286009</t>
+          <t>289340</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>335111</t>
+          <t>338005</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>52,94%</t>
+          <t>53,56%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>62,03%</t>
+          <t>62,57%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>246961</t>
+          <t>247107</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>290031</t>
+          <t>288013</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>39,98%</t>
+          <t>40,0%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>46,95%</t>
+          <t>46,62%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>289224</t>
+          <t>290695</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>343369</t>
+          <t>342775</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>39,13%</t>
+          <t>39,33%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>46,46%</t>
+          <t>46,38%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>543972</t>
+          <t>551504</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>617390</t>
+          <t>619270</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>40,09%</t>
+          <t>40,65%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>45,5%</t>
+          <t>45,64%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>327744</t>
+          <t>329762</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>370814</t>
+          <t>370668</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>53,05%</t>
+          <t>53,38%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>60,02%</t>
+          <t>60,0%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>395675</t>
+          <t>396269</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>449820</t>
+          <t>448349</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>53,54%</t>
+          <t>53,62%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>60,87%</t>
+          <t>60,67%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>739430</t>
+          <t>737550</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>812848</t>
+          <t>805316</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>54,5%</t>
+          <t>54,36%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>59,91%</t>
+          <t>59,35%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP2906_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP2906_2023-Edad-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>16510</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>12401</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>20804</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>43,67%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>32,8%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>55,02%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>18731</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>13796</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>23792</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>39,21%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>28,88%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>49,8%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>20191</t>
+          <t>17154</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>15046</t>
+          <t>12860</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>25183</t>
+          <t>21911</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>44,16%</t>
+          <t>39,13%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>32,91%</t>
+          <t>29,34%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>55,08%</t>
+          <t>49,99%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>38922</t>
+          <t>33664</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>31969</t>
+          <t>27332</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>47074</t>
+          <t>40353</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>41,63%</t>
+          <t>41,23%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>34,19%</t>
+          <t>33,48%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>50,35%</t>
+          <t>49,43%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>21300</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>17006</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>25409</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>56,33%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>44,98%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>67,2%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>50</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>29045</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>23984</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>33980</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>60,79%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>50,2%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>71,12%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>25531</t>
+          <t>26678</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>20539</t>
+          <t>21921</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>30676</t>
+          <t>30972</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>55,84%</t>
+          <t>60,87%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>44,92%</t>
+          <t>50,01%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>67,09%</t>
+          <t>70,66%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>54576</t>
+          <t>47977</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>46424</t>
+          <t>41288</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>61529</t>
+          <t>54309</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>58,37%</t>
+          <t>58,77%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>49,65%</t>
+          <t>50,57%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>65,81%</t>
+          <t>66,52%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>37810</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>37810</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>37810</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>86</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>47776</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>47776</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>47776</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>45722</t>
+          <t>43832</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>45722</t>
+          <t>43832</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>45722</t>
+          <t>43832</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>93498</t>
+          <t>81641</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>93498</t>
+          <t>81641</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>93498</t>
+          <t>81641</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>74665</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>64899</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>84470</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>47,77%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>41,52%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>54,04%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>123</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>76046</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>65293</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>86753</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>48,11%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>41,31%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>54,89%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>131</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>84338</t>
+          <t>69654</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>73150</t>
+          <t>60427</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>95750</t>
+          <t>79057</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>46,58%</t>
+          <t>48,27%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>40,4%</t>
+          <t>41,88%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>52,89%</t>
+          <t>54,79%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>160384</t>
+          <t>144319</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>144189</t>
+          <t>129874</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>174302</t>
+          <t>157074</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>47,3%</t>
+          <t>48,01%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>42,52%</t>
+          <t>43,21%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>51,4%</t>
+          <t>52,26%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>81636</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>71831</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>91402</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>52,23%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>45,96%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>58,48%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>133</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>82006</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>71299</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>92759</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>51,89%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>45,11%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>58,69%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>142</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>96710</t>
+          <t>74635</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>85298</t>
+          <t>65232</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>107898</t>
+          <t>83862</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>53,42%</t>
+          <t>51,73%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>47,11%</t>
+          <t>45,21%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>59,6%</t>
+          <t>58,12%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>178716</t>
+          <t>156271</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>164798</t>
+          <t>143516</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>194911</t>
+          <t>170716</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>52,7%</t>
+          <t>51,99%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>48,6%</t>
+          <t>47,74%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>57,48%</t>
+          <t>56,79%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>273</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>156301</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>156301</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>156301</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>256</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>158052</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>158052</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>158052</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>273</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>181048</t>
+          <t>144289</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>181048</t>
+          <t>144289</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>181048</t>
+          <t>144289</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>339100</t>
+          <t>300590</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>339100</t>
+          <t>300590</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>339100</t>
+          <t>300590</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>86730</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>73961</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>100280</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>43,34%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>36,96%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>50,11%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>91</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>68782</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>57590</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>80408</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>40,1%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>68721</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>58109</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>80131</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>39,7%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>33,57%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>46,88%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>88181</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>74326</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>101320</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>41,5%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>34,98%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>47,68%</t>
+          <t>46,29%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>156963</t>
+          <t>155451</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>137751</t>
+          <t>137458</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>175477</t>
+          <t>172180</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>40,87%</t>
+          <t>41,65%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>35,87%</t>
+          <t>36,83%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>45,69%</t>
+          <t>46,13%</t>
         </is>
       </c>
     </row>
@@ -1519,74 +1519,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>113396</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>99846</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>126165</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>56,66%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>49,89%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>63,04%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>140</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>102746</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>91120</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>113938</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>59,9%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>53,12%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>104385</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>92975</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>114997</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>60,3%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>53,71%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>66,43%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>141</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>124309</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>111170</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>138164</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>58,5%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>52,32%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>65,02%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>281</t>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>227055</t>
+          <t>217781</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>208541</t>
+          <t>201052</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>246267</t>
+          <t>235774</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>59,13%</t>
+          <t>58,35%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>54,31%</t>
+          <t>53,87%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>64,13%</t>
+          <t>63,17%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>231</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>171528</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>171528</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>171528</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>243</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>173106</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>173106</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>173106</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>384018</t>
+          <t>373232</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>384018</t>
+          <t>373232</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>384018</t>
+          <t>373232</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>120543</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>100661</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>137121</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>41,99%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>35,06%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>47,76%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>151</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>104762</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>91311</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>118628</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>43,57%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>37,98%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>49,34%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>143</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>122832</t>
+          <t>110778</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>102837</t>
+          <t>98532</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>141819</t>
+          <t>125196</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>40,97%</t>
+          <t>45,27%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>34,3%</t>
+          <t>40,27%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>47,31%</t>
+          <t>51,17%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>227594</t>
+          <t>231321</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>202198</t>
+          <t>207875</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>250863</t>
+          <t>255724</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>42,13%</t>
+          <t>43,5%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>37,43%</t>
+          <t>39,09%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>46,44%</t>
+          <t>48,09%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>166561</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>149983</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>186443</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>58,01%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>52,24%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>64,94%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>181</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>135657</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>121791</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>149108</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>56,43%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>50,66%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>62,02%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>191</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>176952</t>
+          <t>133909</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>157965</t>
+          <t>119491</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>196947</t>
+          <t>146155</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>59,03%</t>
+          <t>54,73%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>52,69%</t>
+          <t>48,83%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>65,7%</t>
+          <t>59,73%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>312609</t>
+          <t>300470</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>289340</t>
+          <t>276067</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>338005</t>
+          <t>323916</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>57,87%</t>
+          <t>56,5%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>53,56%</t>
+          <t>51,91%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>62,57%</t>
+          <t>60,91%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>334</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>287104</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>287104</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>287104</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>332</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>240419</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>240419</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>240419</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>334</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>299784</t>
+          <t>244687</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>299784</t>
+          <t>244687</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>299784</t>
+          <t>244687</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>540203</t>
+          <t>531791</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>540203</t>
+          <t>531791</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>540203</t>
+          <t>531791</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,72 +2092,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>413</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>298448</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>269880</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>323279</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>43,8%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>39,61%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>47,45%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>401</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>268322</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>247107</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>288013</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>43,43%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>40,0%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>46,62%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>413</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>315541</t>
+          <t>266306</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>290695</t>
+          <t>245993</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>342775</t>
+          <t>285743</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>42,7%</t>
+          <t>43,95%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>39,33%</t>
+          <t>40,6%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>46,38%</t>
+          <t>47,16%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>583863</t>
+          <t>564755</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>551504</t>
+          <t>533428</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>619270</t>
+          <t>595068</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>43,03%</t>
+          <t>43,87%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>40,65%</t>
+          <t>41,44%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>45,64%</t>
+          <t>46,23%</t>
         </is>
       </c>
     </row>
@@ -2205,72 +2205,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>519</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>382893</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>358062</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>411461</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>56,2%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>52,55%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>60,39%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>504</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>349453</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>329762</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>370668</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>56,57%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>53,38%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>60,0%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>519</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>423503</t>
+          <t>339608</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>396269</t>
+          <t>320171</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>448349</t>
+          <t>359921</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>57,3%</t>
+          <t>56,05%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>53,62%</t>
+          <t>52,84%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>60,67%</t>
+          <t>59,4%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>772957</t>
+          <t>722500</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>737550</t>
+          <t>692187</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>805316</t>
+          <t>753827</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>56,97%</t>
+          <t>56,13%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>54,36%</t>
+          <t>53,77%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>59,35%</t>
+          <t>58,56%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>932</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>681341</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>681341</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>681341</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>905</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>617775</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>617775</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>617775</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>932</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>739044</t>
+          <t>605914</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>739044</t>
+          <t>605914</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>739044</t>
+          <t>605914</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1356820</t>
+          <t>1287255</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1356820</t>
+          <t>1287255</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1356820</t>
+          <t>1287255</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
